--- a/questionnaire_templates/025_programming_variables_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/025_programming_variables_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,20 +525,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Programming Variable Types</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Choose a main category for a variable</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,33 +552,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What can a variable hold?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose one of the options</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type</t>
+          <t>programming_variables_quiz_first_question_answer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_question_type</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Variable types answer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Choose all that apply</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,23 +596,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_answer</t>
+          <t>programming_variables_quiz_second_question</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_question_type_answer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is a constant in programming?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Define the term</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +628,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_answer_other</t>
+          <t>programming_variables_quiz_second_question_answer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>first_question_type_answer_other</t>
+          <t>Constant answer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +646,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_second_question</t>
+          <t>programming_variables_quiz_second_question_answer_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>Programming Variables Quiz Second Question Answer 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +674,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_second_question_answer</t>
+          <t>programming_variables_quiz_third_question</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>second_question_answer</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is an array in programming?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Define the term</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_second_question_answer</t>
+          <t>programming_variables_quiz_third_question_answer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>second_question_answer</t>
+          <t>Array answer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +719,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_third_question</t>
+          <t>programming_variables_quiz_third_question_answer_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>Programming Variables Quiz Third Question Answer 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +747,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_third_question_answer</t>
+          <t>programming_variables_quiz_fourth_question</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>third_question_answer</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Can a constant be changed once it's defined?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +774,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_third_question_answer</t>
+          <t>programming_variables_quiz_fourth_question_answer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>third_question_answer</t>
+          <t>Programming Variables Quiz Fourth Question Answer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +792,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_fourth_question</t>
+          <t>programming_variables_quiz_fourth_question_answer_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fourth_question</t>
+          <t>Programming Variables Quiz Fourth Question Answer 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,35 +820,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_fourth_question_answer</t>
+          <t>programming_variables_quiz_fifth_question</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fourth_question_answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is a string in programming?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Define the term</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_fifth_question</t>
+          <t>programming_variables_quiz_fifth_question_answer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fifth_question</t>
+          <t>String answer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +870,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_fifth_question_answer</t>
+          <t>programming_variables_quiz_fifth_question_answer_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fifth_question_answer</t>
+          <t>Programming Variables Quiz Fifth Question Answer 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,35 +893,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_fifth_question_answer</t>
+          <t>programming_variables_quiz_sixth_question</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fifth_question_answer</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Can a string variable be changed after it's defined?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_sixth_question</t>
+          <t>programming_variables_quiz_sixth_question_answer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sixth_question</t>
+          <t>Programming Variables Quiz Sixth Question Answer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,39 +943,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_sixth_question_answer</t>
+          <t>programming_variables_quiz_sixth_question_answer_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sixth_question_answer</t>
+          <t>Programming Variables Quiz Sixth Question Answer 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_answer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sixth_question_answer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +969,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,7 +997,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1005,935 +1014,187 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>data_type</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>Data Type</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_question_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>constant</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>constant</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_question_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_question_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_question_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>array</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>array</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_question_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>object</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_choices</t>
+          <t>programming_variables_quiz_first_question_answer_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
+          <t>programming_variables_quiz_first_question_answer_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>variable</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>variable</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
+          <t>programming_variables_quiz_first_question_answer_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>boolean</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
+          <t>programming_variables_quiz_first_question_answer_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>constant</t>
+          <t>array</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>constant</t>
+          <t>array</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
+          <t>programming_variables_quiz_first_question_answer_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
           <t>object</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_first_question_type_answer_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_second_question_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_third_question_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fourth_question_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_fifth_question_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>constant</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>programming_variables_quiz_sixth_question_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>boolean</t>
         </is>
       </c>
     </row>
